--- a/data/nzd0491/nzd0491.xlsx
+++ b/data/nzd0491/nzd0491.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q467"/>
+  <dimension ref="A1:Q470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27027,7 +27027,7 @@
         <v>354.28</v>
       </c>
       <c r="K467" t="n">
-        <v>357.57</v>
+        <v>355.25</v>
       </c>
       <c r="L467" t="n">
         <v>359.17</v>
@@ -27045,6 +27045,177 @@
         <v>402.11</v>
       </c>
       <c r="Q467" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-08 22:32:39+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>364.48</v>
+      </c>
+      <c r="C468" t="n">
+        <v>374.9</v>
+      </c>
+      <c r="D468" t="n">
+        <v>384.35</v>
+      </c>
+      <c r="E468" t="n">
+        <v>386.35</v>
+      </c>
+      <c r="F468" t="n">
+        <v>374.04</v>
+      </c>
+      <c r="G468" t="n">
+        <v>369.54</v>
+      </c>
+      <c r="H468" t="n">
+        <v>371.19</v>
+      </c>
+      <c r="I468" t="n">
+        <v>363.67</v>
+      </c>
+      <c r="J468" t="n">
+        <v>354.48</v>
+      </c>
+      <c r="K468" t="n">
+        <v>352.45</v>
+      </c>
+      <c r="L468" t="n">
+        <v>360.77</v>
+      </c>
+      <c r="M468" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="N468" t="n">
+        <v>378.57</v>
+      </c>
+      <c r="O468" t="n">
+        <v>389.06</v>
+      </c>
+      <c r="P468" t="n">
+        <v>404.13</v>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>364.34</v>
+      </c>
+      <c r="C469" t="n">
+        <v>374.92</v>
+      </c>
+      <c r="D469" t="n">
+        <v>385.05</v>
+      </c>
+      <c r="E469" t="n">
+        <v>385.02</v>
+      </c>
+      <c r="F469" t="n">
+        <v>372.71</v>
+      </c>
+      <c r="G469" t="n">
+        <v>368.16</v>
+      </c>
+      <c r="H469" t="n">
+        <v>370.62</v>
+      </c>
+      <c r="I469" t="n">
+        <v>364.22</v>
+      </c>
+      <c r="J469" t="n">
+        <v>356.02</v>
+      </c>
+      <c r="K469" t="n">
+        <v>352.45</v>
+      </c>
+      <c r="L469" t="n">
+        <v>360.77</v>
+      </c>
+      <c r="M469" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="N469" t="n">
+        <v>378.57</v>
+      </c>
+      <c r="O469" t="n">
+        <v>389.06</v>
+      </c>
+      <c r="P469" t="n">
+        <v>404.13</v>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-24 22:32:29+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="C470" t="n">
+        <v>375.12</v>
+      </c>
+      <c r="D470" t="n">
+        <v>384.06</v>
+      </c>
+      <c r="E470" t="n">
+        <v>384.35</v>
+      </c>
+      <c r="F470" t="n">
+        <v>371.19</v>
+      </c>
+      <c r="G470" t="n">
+        <v>367.51</v>
+      </c>
+      <c r="H470" t="n">
+        <v>371.81</v>
+      </c>
+      <c r="I470" t="n">
+        <v>366.27</v>
+      </c>
+      <c r="J470" t="n">
+        <v>356.98</v>
+      </c>
+      <c r="K470" t="n">
+        <v>354.16</v>
+      </c>
+      <c r="L470" t="n">
+        <v>363.88</v>
+      </c>
+      <c r="M470" t="n">
+        <v>370.17</v>
+      </c>
+      <c r="N470" t="n">
+        <v>375.79</v>
+      </c>
+      <c r="O470" t="n">
+        <v>392.42</v>
+      </c>
+      <c r="P470" t="n">
+        <v>409.27</v>
+      </c>
+      <c r="Q470" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27061,7 +27232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32364,6 +32535,36 @@
       </c>
       <c r="B530" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-07-08 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-07-24 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>0.23</v>
       </c>
     </row>
   </sheetData>
@@ -32532,28 +32733,28 @@
         <v>0.153</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2877948329226885</v>
+        <v>-0.2947109545821475</v>
       </c>
       <c r="J2" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K2" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05237427804892736</v>
+        <v>0.05538224403805803</v>
       </c>
       <c r="M2" t="n">
-        <v>7.795415892683561</v>
+        <v>7.779613905876844</v>
       </c>
       <c r="N2" t="n">
-        <v>85.03803006015012</v>
+        <v>84.68911108011578</v>
       </c>
       <c r="O2" t="n">
-        <v>9.221606696240634</v>
+        <v>9.20266869337997</v>
       </c>
       <c r="P2" t="n">
-        <v>377.5933468821265</v>
+        <v>377.6657980844827</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32610,28 +32811,28 @@
         <v>0.0901</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09220905406914141</v>
+        <v>-0.09504271204005672</v>
       </c>
       <c r="J3" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K3" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005251610720559574</v>
+        <v>0.005652802127563139</v>
       </c>
       <c r="M3" t="n">
-        <v>8.008558904886016</v>
+        <v>7.971297091692206</v>
       </c>
       <c r="N3" t="n">
-        <v>91.41655258104676</v>
+        <v>90.86354885532533</v>
       </c>
       <c r="O3" t="n">
-        <v>9.561200373438826</v>
+        <v>9.532237347827914</v>
       </c>
       <c r="P3" t="n">
-        <v>379.7305481907049</v>
+        <v>379.7602245674308</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32688,28 +32889,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3205213655329354</v>
+        <v>-0.313282990957764</v>
       </c>
       <c r="J4" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K4" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05318912972975598</v>
+        <v>0.05150613317507102</v>
       </c>
       <c r="M4" t="n">
-        <v>8.608634076702938</v>
+        <v>8.581304344709544</v>
       </c>
       <c r="N4" t="n">
-        <v>103.8033350581101</v>
+        <v>103.3539304284271</v>
       </c>
       <c r="O4" t="n">
-        <v>10.1883921723749</v>
+        <v>10.16631351220427</v>
       </c>
       <c r="P4" t="n">
-        <v>387.1966820585213</v>
+        <v>387.1208761916309</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32766,28 +32967,28 @@
         <v>0.091</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2697017972831169</v>
+        <v>-0.2620470201526607</v>
       </c>
       <c r="J5" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K5" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04249643625506938</v>
+        <v>0.04064923807971699</v>
       </c>
       <c r="M5" t="n">
-        <v>7.757509010196191</v>
+        <v>7.740741104469285</v>
       </c>
       <c r="N5" t="n">
-        <v>92.93880666266648</v>
+        <v>92.58863377701446</v>
       </c>
       <c r="O5" t="n">
-        <v>9.640477512170571</v>
+        <v>9.62229877820339</v>
       </c>
       <c r="P5" t="n">
-        <v>386.2563147812591</v>
+        <v>386.1761646995534</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32844,28 +33045,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.272545882190312</v>
+        <v>-0.2789139376058582</v>
       </c>
       <c r="J6" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K6" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05735645444151172</v>
+        <v>0.06054672647958204</v>
       </c>
       <c r="M6" t="n">
-        <v>6.426170995689223</v>
+        <v>6.41587736229683</v>
       </c>
       <c r="N6" t="n">
-        <v>69.22866774801008</v>
+        <v>68.96030283305502</v>
       </c>
       <c r="O6" t="n">
-        <v>8.32037665902272</v>
+        <v>8.304234030484391</v>
       </c>
       <c r="P6" t="n">
-        <v>385.0638907523449</v>
+        <v>385.1305866128487</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32922,28 +33123,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08045240087780001</v>
+        <v>-0.09390950967948718</v>
       </c>
       <c r="J7" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K7" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004048619359047656</v>
+        <v>0.005538879452595014</v>
       </c>
       <c r="M7" t="n">
-        <v>7.195001049463114</v>
+        <v>7.218597270573418</v>
       </c>
       <c r="N7" t="n">
-        <v>90.13514583697996</v>
+        <v>90.30181371779402</v>
       </c>
       <c r="O7" t="n">
-        <v>9.493953119590383</v>
+        <v>9.50272664648384</v>
       </c>
       <c r="P7" t="n">
-        <v>381.4045104344016</v>
+        <v>381.5457134438677</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33000,28 +33201,28 @@
         <v>0.0788</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1199105017633771</v>
+        <v>-0.1286950050816108</v>
       </c>
       <c r="J8" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K8" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009893655849006699</v>
+        <v>0.01149176465584179</v>
       </c>
       <c r="M8" t="n">
-        <v>7.478930957053671</v>
+        <v>7.484036345301945</v>
       </c>
       <c r="N8" t="n">
-        <v>81.59828063726005</v>
+        <v>81.39376928733</v>
       </c>
       <c r="O8" t="n">
-        <v>9.033176663680393</v>
+        <v>9.021849549140686</v>
       </c>
       <c r="P8" t="n">
-        <v>381.5080666658076</v>
+        <v>381.6000495773142</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33078,28 +33279,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2112424621939649</v>
+        <v>-0.2174279772706524</v>
       </c>
       <c r="J9" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K9" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02803580582135157</v>
+        <v>0.0299987278268834</v>
       </c>
       <c r="M9" t="n">
-        <v>7.59858328597312</v>
+        <v>7.580157919156045</v>
       </c>
       <c r="N9" t="n">
-        <v>87.72859784252891</v>
+        <v>87.33222540096196</v>
       </c>
       <c r="O9" t="n">
-        <v>9.366354565279329</v>
+        <v>9.345171234437705</v>
       </c>
       <c r="P9" t="n">
-        <v>375.3585264894197</v>
+        <v>375.4232857764756</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33156,28 +33357,28 @@
         <v>0.1006</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5826176121572341</v>
+        <v>-0.5885801270512395</v>
       </c>
       <c r="J10" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K10" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1922638213494091</v>
+        <v>0.197334325489689</v>
       </c>
       <c r="M10" t="n">
-        <v>7.348471102099638</v>
+        <v>7.329300441817616</v>
       </c>
       <c r="N10" t="n">
-        <v>80.8687456257064</v>
+        <v>80.50399892625155</v>
       </c>
       <c r="O10" t="n">
-        <v>8.992705133924185</v>
+        <v>8.972402071143019</v>
       </c>
       <c r="P10" t="n">
-        <v>376.1988401479738</v>
+        <v>376.2612671336555</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33234,28 +33435,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4019669038444031</v>
+        <v>-0.414352144751647</v>
       </c>
       <c r="J11" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K11" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09942992143858642</v>
+        <v>0.1056248419086981</v>
       </c>
       <c r="M11" t="n">
-        <v>7.405713516638071</v>
+        <v>7.41996025544442</v>
       </c>
       <c r="N11" t="n">
-        <v>82.98938263694801</v>
+        <v>83.05524197594097</v>
       </c>
       <c r="O11" t="n">
-        <v>9.109850857009022</v>
+        <v>9.113464872151589</v>
       </c>
       <c r="P11" t="n">
-        <v>372.9974726146338</v>
+        <v>373.1271017437194</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33312,28 +33513,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6495344207851929</v>
+        <v>-0.6494588558388918</v>
       </c>
       <c r="J12" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K12" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2552735936605345</v>
+        <v>0.2578341547389047</v>
       </c>
       <c r="M12" t="n">
-        <v>6.866633651869824</v>
+        <v>6.831553720177887</v>
       </c>
       <c r="N12" t="n">
-        <v>69.79699504568192</v>
+        <v>69.36462024963305</v>
       </c>
       <c r="O12" t="n">
-        <v>8.354459590283618</v>
+        <v>8.328542504522208</v>
       </c>
       <c r="P12" t="n">
-        <v>379.0846818011962</v>
+        <v>379.0838733468815</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33390,28 +33591,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4911408497306856</v>
+        <v>-0.4900280799776651</v>
       </c>
       <c r="J13" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K13" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1293701871041263</v>
+        <v>0.1304085275615176</v>
       </c>
       <c r="M13" t="n">
-        <v>7.777483426382324</v>
+        <v>7.73423537759107</v>
       </c>
       <c r="N13" t="n">
-        <v>92.0561835833709</v>
+        <v>91.47984594298542</v>
       </c>
       <c r="O13" t="n">
-        <v>9.594591371359746</v>
+        <v>9.564509707401912</v>
       </c>
       <c r="P13" t="n">
-        <v>380.8717887215006</v>
+        <v>380.8601237523276</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33468,28 +33669,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.388994423117471</v>
+        <v>-0.3835541065421175</v>
       </c>
       <c r="J14" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K14" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08805539982050548</v>
+        <v>0.08679223147967596</v>
       </c>
       <c r="M14" t="n">
-        <v>7.923149538290321</v>
+        <v>7.899812540060791</v>
       </c>
       <c r="N14" t="n">
-        <v>89.09907988934228</v>
+        <v>88.65940799391724</v>
       </c>
       <c r="O14" t="n">
-        <v>9.439230895011642</v>
+        <v>9.415912488650116</v>
       </c>
       <c r="P14" t="n">
-        <v>383.6280130871448</v>
+        <v>383.5710722017714</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33546,28 +33747,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2600322487821015</v>
+        <v>-0.2490566829494604</v>
       </c>
       <c r="J15" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K15" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03614283430980203</v>
+        <v>0.03353931905854179</v>
       </c>
       <c r="M15" t="n">
-        <v>8.229026843243057</v>
+        <v>8.229114916045972</v>
       </c>
       <c r="N15" t="n">
-        <v>102.8678172988475</v>
+        <v>102.7180478261839</v>
       </c>
       <c r="O15" t="n">
-        <v>10.1423773001623</v>
+        <v>10.13499125930476</v>
       </c>
       <c r="P15" t="n">
-        <v>388.2517019250015</v>
+        <v>388.1368763413768</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33624,28 +33825,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3898760121400416</v>
+        <v>-0.3650199867849892</v>
       </c>
       <c r="J16" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K16" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05475375362191726</v>
+        <v>0.0481612012694963</v>
       </c>
       <c r="M16" t="n">
-        <v>10.1268630854365</v>
+        <v>10.1773157573614</v>
       </c>
       <c r="N16" t="n">
-        <v>149.7974993733445</v>
+        <v>151.4236735078134</v>
       </c>
       <c r="O16" t="n">
-        <v>12.23917886842677</v>
+        <v>12.30543268267367</v>
       </c>
       <c r="P16" t="n">
-        <v>396.1636508014639</v>
+        <v>395.9035250250815</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33683,7 +33884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q467"/>
+  <dimension ref="A1:Q470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74221,7 +74422,7 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>-45.4997930586876,166.7235058945346</t>
+          <t>-45.49980571489116,166.72352940436477</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -74250,6 +74451,267 @@
         </is>
       </c>
       <c r="Q467" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-08 22:32:39+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>-45.50401148744418,166.71822011574812</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>-45.503491554026866,166.7187562127088</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>-45.50297800873911,166.7193007155222</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-45.502513546796585,166.71990977578025</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>-45.50214336627768,166.72064283780784</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>-45.50172490774404,166.7213026786958</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>-45.50126370641789,166.7218628786833</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>-45.50079869506616,166.72242879936303</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>-45.50032937487931,166.7230295673701</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>-45.49982098961385,166.7235577783121</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>-45.49925696102734,166.7239800105595</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>-45.49869950072225,166.72439997932722</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>-45.49811203329469,166.72475273285463</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>-45.49752177619846,166.725111712242</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>-45.496908222275785,166.7254225364185</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>-45.504012409884744,166.71822132891265</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>-45.50349142225016,166.7187560394002</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>-45.50297339657291,166.7192946497414</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>-45.502522309870784,166.71992130074864</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>-45.502152129300455,166.72065436279695</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>-45.50173383771046,166.72131488199048</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>-45.50126707819408,166.72186834929803</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>-45.500795694633915,166.7224232258648</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>-45.50032097372995,166.72301396162578</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>-45.49982098961385,166.7235577783121</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>-45.49925696102734,166.7239800105595</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>-45.49869950072225,166.72439997932722</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>-45.49811203329469,166.72475273285463</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>-45.49752177619846,166.725111712242</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>-45.496908222275785,166.7254225364185</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-24 22:32:29+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>-45.50401366176836,166.71822297535022</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>-45.5034901044831,166.7187543063142</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>-45.50297991949359,166.7193032284888</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-45.50252672435139,166.71992710656116</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-45.5021621441824,166.72066753421745</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>-45.501738043853685,166.72132062992048</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>-45.5012600388716,166.72185692819087</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>-45.50078451120252,166.72240245192222</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>-45.50031573664885,166.723004233372</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>-45.499811661123246,166.72354044993529</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>-45.49924013112689,166.72394834845153</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>-45.49868763401692,166.72437643228204</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>-45.49812617152265,166.72478196383983</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>-45.497504688335944,166.7250763830042</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>-45.49688208200741,166.7253684915768</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0491/nzd0491.xlsx
+++ b/data/nzd0491/nzd0491.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q470"/>
+  <dimension ref="A1:Q473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26982,7 +26982,7 @@
         <v>372.14</v>
       </c>
       <c r="O466" t="n">
-        <v>390.18</v>
+        <v>392.84</v>
       </c>
       <c r="P466" t="n">
         <v>402.68</v>
@@ -27039,7 +27039,7 @@
         <v>376.82</v>
       </c>
       <c r="O467" t="n">
-        <v>389.96</v>
+        <v>392.82</v>
       </c>
       <c r="P467" t="n">
         <v>402.11</v>
@@ -27096,7 +27096,7 @@
         <v>378.57</v>
       </c>
       <c r="O468" t="n">
-        <v>389.06</v>
+        <v>393.24</v>
       </c>
       <c r="P468" t="n">
         <v>404.13</v>
@@ -27153,7 +27153,7 @@
         <v>378.57</v>
       </c>
       <c r="O469" t="n">
-        <v>389.06</v>
+        <v>393.24</v>
       </c>
       <c r="P469" t="n">
         <v>404.13</v>
@@ -27210,12 +27210,183 @@
         <v>375.79</v>
       </c>
       <c r="O470" t="n">
-        <v>392.42</v>
+        <v>398.56</v>
       </c>
       <c r="P470" t="n">
         <v>409.27</v>
       </c>
       <c r="Q470" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-09 22:32:57+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>364.24</v>
+      </c>
+      <c r="C471" t="n">
+        <v>374.83</v>
+      </c>
+      <c r="D471" t="n">
+        <v>384.1</v>
+      </c>
+      <c r="E471" t="n">
+        <v>382.8</v>
+      </c>
+      <c r="F471" t="n">
+        <v>370.22</v>
+      </c>
+      <c r="G471" t="n">
+        <v>367</v>
+      </c>
+      <c r="H471" t="n">
+        <v>372.54</v>
+      </c>
+      <c r="I471" t="n">
+        <v>366.99</v>
+      </c>
+      <c r="J471" t="n">
+        <v>357.7</v>
+      </c>
+      <c r="K471" t="n">
+        <v>354.81</v>
+      </c>
+      <c r="L471" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="M471" t="n">
+        <v>370.02</v>
+      </c>
+      <c r="N471" t="n">
+        <v>375.79</v>
+      </c>
+      <c r="O471" t="n">
+        <v>396.98</v>
+      </c>
+      <c r="P471" t="n">
+        <v>404.99</v>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>364.06</v>
+      </c>
+      <c r="C472" t="n">
+        <v>375.07</v>
+      </c>
+      <c r="D472" t="n">
+        <v>384.18</v>
+      </c>
+      <c r="E472" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="F472" t="n">
+        <v>368.46</v>
+      </c>
+      <c r="G472" t="n">
+        <v>365.72</v>
+      </c>
+      <c r="H472" t="n">
+        <v>371.86</v>
+      </c>
+      <c r="I472" t="n">
+        <v>366.99</v>
+      </c>
+      <c r="J472" t="n">
+        <v>357.7</v>
+      </c>
+      <c r="K472" t="n">
+        <v>354.81</v>
+      </c>
+      <c r="L472" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="M472" t="n">
+        <v>370.02</v>
+      </c>
+      <c r="N472" t="n">
+        <v>375.79</v>
+      </c>
+      <c r="O472" t="n">
+        <v>396.98</v>
+      </c>
+      <c r="P472" t="n">
+        <v>404.99</v>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>365.16</v>
+      </c>
+      <c r="C473" t="n">
+        <v>377.31</v>
+      </c>
+      <c r="D473" t="n">
+        <v>386.24</v>
+      </c>
+      <c r="E473" t="n">
+        <v>380.9</v>
+      </c>
+      <c r="F473" t="n">
+        <v>368.01</v>
+      </c>
+      <c r="G473" t="n">
+        <v>366.18</v>
+      </c>
+      <c r="H473" t="n">
+        <v>373.58</v>
+      </c>
+      <c r="I473" t="n">
+        <v>369.46</v>
+      </c>
+      <c r="J473" t="n">
+        <v>361.28</v>
+      </c>
+      <c r="K473" t="n">
+        <v>358.54</v>
+      </c>
+      <c r="L473" t="n">
+        <v>368.47</v>
+      </c>
+      <c r="M473" t="n">
+        <v>372.08</v>
+      </c>
+      <c r="N473" t="n">
+        <v>376.91</v>
+      </c>
+      <c r="O473" t="n">
+        <v>398.32</v>
+      </c>
+      <c r="P473" t="n">
+        <v>406.66</v>
+      </c>
+      <c r="Q473" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27232,7 +27403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B533"/>
+  <dimension ref="A1:B536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32565,6 +32736,36 @@
       </c>
       <c r="B533" t="n">
         <v>0.23</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-08-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -32733,28 +32934,28 @@
         <v>0.153</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2947109545821475</v>
+        <v>-0.3011717529956423</v>
       </c>
       <c r="J2" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K2" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05538224403805803</v>
+        <v>0.05832903891622443</v>
       </c>
       <c r="M2" t="n">
-        <v>7.779613905876844</v>
+        <v>7.761537422042284</v>
       </c>
       <c r="N2" t="n">
-        <v>84.68911108011578</v>
+        <v>84.32568614506513</v>
       </c>
       <c r="O2" t="n">
-        <v>9.20266869337997</v>
+        <v>9.182901836841399</v>
       </c>
       <c r="P2" t="n">
-        <v>377.6657980844827</v>
+        <v>377.7337195789061</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32811,28 +33012,28 @@
         <v>0.0901</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09504271204005672</v>
+        <v>-0.0968480507757912</v>
       </c>
       <c r="J3" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K3" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005652802127563139</v>
+        <v>0.005947268870191036</v>
       </c>
       <c r="M3" t="n">
-        <v>7.971297091692206</v>
+        <v>7.930097584751322</v>
       </c>
       <c r="N3" t="n">
-        <v>90.86354885532533</v>
+        <v>90.30644385604148</v>
       </c>
       <c r="O3" t="n">
-        <v>9.532237347827914</v>
+        <v>9.502970264924619</v>
       </c>
       <c r="P3" t="n">
-        <v>379.7602245674308</v>
+        <v>379.7791934550204</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32889,28 +33090,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.313282990957764</v>
+        <v>-0.3058185004292092</v>
       </c>
       <c r="J4" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K4" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05150613317507102</v>
+        <v>0.04973422891631973</v>
       </c>
       <c r="M4" t="n">
-        <v>8.581304344709544</v>
+        <v>8.554956688094157</v>
       </c>
       <c r="N4" t="n">
-        <v>103.3539304284271</v>
+        <v>102.9348244638162</v>
       </c>
       <c r="O4" t="n">
-        <v>10.16631351220427</v>
+        <v>10.1456800887775</v>
       </c>
       <c r="P4" t="n">
-        <v>387.1208761916309</v>
+        <v>387.0424102388868</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32967,28 +33168,28 @@
         <v>0.091</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2620470201526607</v>
+        <v>-0.2587312128112764</v>
       </c>
       <c r="J5" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K5" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04064923807971699</v>
+        <v>0.04017179876226307</v>
       </c>
       <c r="M5" t="n">
-        <v>7.740741104469285</v>
+        <v>7.706216510769585</v>
       </c>
       <c r="N5" t="n">
-        <v>92.58863377701446</v>
+        <v>92.04986488033289</v>
       </c>
       <c r="O5" t="n">
-        <v>9.62229877820339</v>
+        <v>9.594262081073921</v>
       </c>
       <c r="P5" t="n">
-        <v>386.1761646995534</v>
+        <v>386.1413224443966</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33045,28 +33246,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2789139376058582</v>
+        <v>-0.289625805296759</v>
       </c>
       <c r="J6" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K6" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06054672647958204</v>
+        <v>0.06538390696086116</v>
       </c>
       <c r="M6" t="n">
-        <v>6.41587736229683</v>
+        <v>6.428564249162425</v>
       </c>
       <c r="N6" t="n">
-        <v>68.96030283305502</v>
+        <v>69.0065276742114</v>
       </c>
       <c r="O6" t="n">
-        <v>8.304234030484391</v>
+        <v>8.307016773439873</v>
       </c>
       <c r="P6" t="n">
-        <v>385.1305866128487</v>
+        <v>385.2431651901932</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33123,28 +33324,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09390950967948718</v>
+        <v>-0.1094913441854067</v>
       </c>
       <c r="J7" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K7" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005538879452595014</v>
+        <v>0.007532894886154495</v>
       </c>
       <c r="M7" t="n">
-        <v>7.218597270573418</v>
+        <v>7.25364406189405</v>
       </c>
       <c r="N7" t="n">
-        <v>90.30181371779402</v>
+        <v>90.73987345173354</v>
       </c>
       <c r="O7" t="n">
-        <v>9.50272664648384</v>
+        <v>9.525747920858159</v>
       </c>
       <c r="P7" t="n">
-        <v>381.5457134438677</v>
+        <v>381.7097915940084</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33201,28 +33402,28 @@
         <v>0.0788</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1286950050816108</v>
+        <v>-0.1354065293006768</v>
       </c>
       <c r="J8" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K8" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01149176465584179</v>
+        <v>0.01284897958012565</v>
       </c>
       <c r="M8" t="n">
-        <v>7.484036345301945</v>
+        <v>7.477312368411966</v>
       </c>
       <c r="N8" t="n">
-        <v>81.39376928733</v>
+        <v>81.06762541631645</v>
       </c>
       <c r="O8" t="n">
-        <v>9.021849549140686</v>
+        <v>9.003756183744452</v>
       </c>
       <c r="P8" t="n">
-        <v>381.6000495773142</v>
+        <v>381.6705790628288</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33279,28 +33480,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2174279772706524</v>
+        <v>-0.2196145575227292</v>
       </c>
       <c r="J9" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K9" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0299987278268834</v>
+        <v>0.03098539123571142</v>
       </c>
       <c r="M9" t="n">
-        <v>7.580157919156045</v>
+        <v>7.542502041890416</v>
       </c>
       <c r="N9" t="n">
-        <v>87.33222540096196</v>
+        <v>86.80582499009763</v>
       </c>
       <c r="O9" t="n">
-        <v>9.345171234437705</v>
+        <v>9.316964365612742</v>
       </c>
       <c r="P9" t="n">
-        <v>375.4232857764756</v>
+        <v>375.4462578224095</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33357,28 +33558,28 @@
         <v>0.1006</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5885801270512395</v>
+        <v>-0.5905406945615503</v>
       </c>
       <c r="J10" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K10" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L10" t="n">
-        <v>0.197334325489689</v>
+        <v>0.2005084300041697</v>
       </c>
       <c r="M10" t="n">
-        <v>7.329300441817616</v>
+        <v>7.29520371454611</v>
       </c>
       <c r="N10" t="n">
-        <v>80.50399892625155</v>
+        <v>80.02656806334208</v>
       </c>
       <c r="O10" t="n">
-        <v>8.972402071143019</v>
+        <v>8.9457569866022</v>
       </c>
       <c r="P10" t="n">
-        <v>376.2612671336555</v>
+        <v>376.281860660541</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33435,28 +33636,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.414352144751647</v>
+        <v>-0.4216596791358171</v>
       </c>
       <c r="J11" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K11" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1056248419086981</v>
+        <v>0.1100227917668161</v>
       </c>
       <c r="M11" t="n">
-        <v>7.41996025544442</v>
+        <v>7.408609263868307</v>
       </c>
       <c r="N11" t="n">
-        <v>83.05524197594097</v>
+        <v>82.77013263341782</v>
       </c>
       <c r="O11" t="n">
-        <v>9.113464872151589</v>
+        <v>9.097809221643297</v>
       </c>
       <c r="P11" t="n">
-        <v>373.1271017437194</v>
+        <v>373.2038876615454</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33513,28 +33714,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6494588558388918</v>
+        <v>-0.6446962705298237</v>
       </c>
       <c r="J12" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K12" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2578341547389047</v>
+        <v>0.2573027430586131</v>
       </c>
       <c r="M12" t="n">
-        <v>6.831553720177887</v>
+        <v>6.813930330908522</v>
       </c>
       <c r="N12" t="n">
-        <v>69.36462024963305</v>
+        <v>69.04480362036199</v>
       </c>
       <c r="O12" t="n">
-        <v>8.328542504522208</v>
+        <v>8.309320286302725</v>
       </c>
       <c r="P12" t="n">
-        <v>379.0838733468815</v>
+        <v>379.0338090570882</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33591,28 +33792,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4900280799776651</v>
+        <v>-0.4864049084286532</v>
       </c>
       <c r="J13" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K13" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1304085275615176</v>
+        <v>0.1302028174319716</v>
       </c>
       <c r="M13" t="n">
-        <v>7.73423537759107</v>
+        <v>7.70625617300707</v>
       </c>
       <c r="N13" t="n">
-        <v>91.47984594298542</v>
+        <v>90.95923341246362</v>
       </c>
       <c r="O13" t="n">
-        <v>9.564509707401912</v>
+        <v>9.537255025030191</v>
       </c>
       <c r="P13" t="n">
-        <v>380.8601237523276</v>
+        <v>380.8220406048936</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33669,28 +33870,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3835541065421175</v>
+        <v>-0.3800550732779919</v>
       </c>
       <c r="J14" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K14" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08679223147967596</v>
+        <v>0.08637604326720416</v>
       </c>
       <c r="M14" t="n">
-        <v>7.899812540060791</v>
+        <v>7.866847554839163</v>
       </c>
       <c r="N14" t="n">
-        <v>88.65940799391724</v>
+        <v>88.14659295511836</v>
       </c>
       <c r="O14" t="n">
-        <v>9.415912488650116</v>
+        <v>9.388641699155334</v>
       </c>
       <c r="P14" t="n">
-        <v>383.5710722017714</v>
+        <v>383.534303812091</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33747,28 +33948,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2490566829494604</v>
+        <v>-0.2215044011147309</v>
       </c>
       <c r="J15" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K15" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03353931905854179</v>
+        <v>0.02643905074894526</v>
       </c>
       <c r="M15" t="n">
-        <v>8.229114916045972</v>
+        <v>8.313687059426544</v>
       </c>
       <c r="N15" t="n">
-        <v>102.7180478261839</v>
+        <v>104.5767397846342</v>
       </c>
       <c r="O15" t="n">
-        <v>10.13499125930476</v>
+        <v>10.22627692685047</v>
       </c>
       <c r="P15" t="n">
-        <v>388.1368763413768</v>
+        <v>387.8480752136478</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33825,28 +34026,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3650199867849892</v>
+        <v>-0.3413044924024208</v>
       </c>
       <c r="J16" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K16" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0481612012694963</v>
+        <v>0.042279939986543</v>
       </c>
       <c r="M16" t="n">
-        <v>10.1773157573614</v>
+        <v>10.22242394550169</v>
       </c>
       <c r="N16" t="n">
-        <v>151.4236735078134</v>
+        <v>152.8282440091991</v>
       </c>
       <c r="O16" t="n">
-        <v>12.30543268267367</v>
+        <v>12.36237210284495</v>
       </c>
       <c r="P16" t="n">
-        <v>395.9035250250815</v>
+        <v>395.6544491586064</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33884,7 +34085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q470"/>
+  <dimension ref="A1:Q473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74355,7 +74556,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>-45.4975160802454,166.72509993582696</t>
+          <t>-45.49750255235244,166.72507196685103</t>
         </is>
       </c>
       <c r="P466" t="inlineStr">
@@ -74442,7 +74643,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>-45.4975171990934,166.72510224905116</t>
+          <t>-45.49750265406593,166.72507217714403</t>
         </is>
       </c>
       <c r="P467" t="inlineStr">
@@ -74529,7 +74730,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>-45.49752177619846,166.725111712242</t>
+          <t>-45.49750051808229,166.72506776099118</t>
         </is>
       </c>
       <c r="P468" t="inlineStr">
@@ -74616,7 +74817,7 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>-45.49752177619846,166.725111712242</t>
+          <t>-45.49750051808229,166.72506776099118</t>
         </is>
       </c>
       <c r="P469" t="inlineStr">
@@ -74703,7 +74904,7 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t>-45.497504688335944,166.7250763830042</t>
+          <t>-45.49747346227595,166.7250118230851</t>
         </is>
       </c>
       <c r="P470" t="inlineStr">
@@ -74712,6 +74913,267 @@
         </is>
       </c>
       <c r="Q470" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-09 22:32:57+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>-45.50401306877086,166.71822219545874</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>-45.50349201524532,166.71875681928893</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>-45.50297965594127,166.7193028818727</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-45.50253693695485,166.71994053792193</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-45.50216853525772,166.72067593966585</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>-45.50174134405818,166.72132513983536</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>-45.50125572063126,166.7218499219669</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>-45.500780583362385,166.72239515571025</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>-45.500311808837544,166.72299693718287</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>-45.49980811520515,166.72353386312687</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>-45.499238670009746,166.72394559965207</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>-45.498688418160576,166.72437798825388</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>-45.49812617152265,166.72478196383983</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>-45.497481497649595,166.72502843621683</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>-45.49690384861381,166.72541349389275</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>-45.504014254765856,166.71822375524175</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>-45.50349043392486,166.7187547395857</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>-45.50297912883658,166.71930218864054</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-45.50254273507751,166.71994816347086</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>-45.502180131434265,166.72069119079362</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>-45.501749626923726,166.72133645883983</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>-45.501259743101734,166.72185644831248</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>-45.500780583362385,166.72239515571025</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>-45.500311808837544,166.72299693718287</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>-45.49980811520515,166.72353386312687</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>-45.499238670009746,166.72394559965207</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>-45.498688418160576,166.72437798825388</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>-45.49812617152265,166.72478196383983</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>-45.497481497649595,166.72502843621683</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>-45.49690384861381,166.72541349389275</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>-45.504007007018416,166.71821422323538</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>-45.50347567493237,166.71873532902782</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>-45.502965555889745,166.7192843379164</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-45.50254945562822,166.7199570021772</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-45.502183096365506,166.7206950902307</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>-45.50174665026903,166.72133239107222</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>-45.50124956861699,166.72183994049902</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>-45.50076710868549,166.72237012565765</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>-45.500292278880735,166.72296065892462</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>-45.49978776708396,166.72349606499677</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>-45.499215292127644,166.72390161888063</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>-45.49867764925267,166.72435661957795</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>-45.49812047554673,166.724770187326</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>-45.497474682839176,166.72501434659847</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>-45.49689535557069,166.7253959345736</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0491/nzd0491.xlsx
+++ b/data/nzd0491/nzd0491.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q473"/>
+  <dimension ref="A1:Q474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27389,6 +27389,63 @@
       <c r="Q473" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>368.01</v>
+      </c>
+      <c r="C474" t="n">
+        <v>376.87</v>
+      </c>
+      <c r="D474" t="n">
+        <v>387.46</v>
+      </c>
+      <c r="E474" t="n">
+        <v>379</v>
+      </c>
+      <c r="F474" t="n">
+        <v>364.03</v>
+      </c>
+      <c r="G474" t="n">
+        <v>360.87</v>
+      </c>
+      <c r="H474" t="n">
+        <v>373.37</v>
+      </c>
+      <c r="I474" t="n">
+        <v>372.66</v>
+      </c>
+      <c r="J474" t="n">
+        <v>364.85</v>
+      </c>
+      <c r="K474" t="n">
+        <v>356.83</v>
+      </c>
+      <c r="L474" t="n">
+        <v>367.35</v>
+      </c>
+      <c r="M474" t="n">
+        <v>369.82</v>
+      </c>
+      <c r="N474" t="n">
+        <v>368.41</v>
+      </c>
+      <c r="O474" t="n">
+        <v>394.99</v>
+      </c>
+      <c r="P474" t="n">
+        <v>404.58</v>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27403,7 +27460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B536"/>
+  <dimension ref="A1:B537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32766,6 +32823,16 @@
       </c>
       <c r="B536" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -32934,28 +33001,28 @@
         <v>0.153</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3011717529956423</v>
+        <v>-0.3018366749812602</v>
       </c>
       <c r="J2" t="n">
+        <v>473</v>
+      </c>
+      <c r="K2" t="n">
         <v>472</v>
       </c>
-      <c r="K2" t="n">
-        <v>471</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.05832903891622443</v>
+        <v>0.05881935754543477</v>
       </c>
       <c r="M2" t="n">
-        <v>7.761537422042284</v>
+        <v>7.748300342230506</v>
       </c>
       <c r="N2" t="n">
-        <v>84.32568614506513</v>
+        <v>84.15262942310565</v>
       </c>
       <c r="O2" t="n">
-        <v>9.182901836841399</v>
+        <v>9.173474228617293</v>
       </c>
       <c r="P2" t="n">
-        <v>377.7337195789061</v>
+        <v>377.7407354082399</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33012,28 +33079,28 @@
         <v>0.0901</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0968480507757912</v>
+        <v>-0.09697279353882804</v>
       </c>
       <c r="J3" t="n">
+        <v>473</v>
+      </c>
+      <c r="K3" t="n">
         <v>472</v>
       </c>
-      <c r="K3" t="n">
-        <v>471</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.005947268870191036</v>
+        <v>0.005989507730841059</v>
       </c>
       <c r="M3" t="n">
-        <v>7.930097584751322</v>
+        <v>7.913928688273062</v>
       </c>
       <c r="N3" t="n">
-        <v>90.30644385604148</v>
+        <v>90.11531378570878</v>
       </c>
       <c r="O3" t="n">
-        <v>9.502970264924619</v>
+        <v>9.492908605148834</v>
       </c>
       <c r="P3" t="n">
-        <v>379.7791934550204</v>
+        <v>379.7805093769956</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33090,28 +33157,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3058185004292092</v>
+        <v>-0.3023022730763528</v>
       </c>
       <c r="J4" t="n">
+        <v>473</v>
+      </c>
+      <c r="K4" t="n">
         <v>472</v>
       </c>
-      <c r="K4" t="n">
-        <v>471</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.04973422891631973</v>
+        <v>0.04879260176253142</v>
       </c>
       <c r="M4" t="n">
-        <v>8.554956688094157</v>
+        <v>8.550049379757848</v>
       </c>
       <c r="N4" t="n">
-        <v>102.9348244638162</v>
+        <v>102.8733814718897</v>
       </c>
       <c r="O4" t="n">
-        <v>10.1456800887775</v>
+        <v>10.14265159965035</v>
       </c>
       <c r="P4" t="n">
-        <v>387.0424102388868</v>
+        <v>387.0053172586582</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33168,28 +33235,28 @@
         <v>0.091</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2587312128112764</v>
+        <v>-0.2588103525350041</v>
       </c>
       <c r="J5" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K5" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04017179876226307</v>
+        <v>0.04037133325778275</v>
       </c>
       <c r="M5" t="n">
-        <v>7.706216510769585</v>
+        <v>7.690390983740863</v>
       </c>
       <c r="N5" t="n">
-        <v>92.04986488033289</v>
+        <v>91.85533548625398</v>
       </c>
       <c r="O5" t="n">
-        <v>9.594262081073921</v>
+        <v>9.584118920707004</v>
       </c>
       <c r="P5" t="n">
-        <v>386.1413224443966</v>
+        <v>386.1421571478189</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33246,28 +33313,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.289625805296759</v>
+        <v>-0.2951014500911406</v>
       </c>
       <c r="J6" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K6" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06538390696086116</v>
+        <v>0.06765132905276072</v>
       </c>
       <c r="M6" t="n">
-        <v>6.428564249162425</v>
+        <v>6.442488734984306</v>
       </c>
       <c r="N6" t="n">
-        <v>69.0065276742114</v>
+        <v>69.23978144678846</v>
       </c>
       <c r="O6" t="n">
-        <v>8.307016773439873</v>
+        <v>8.321044492537487</v>
       </c>
       <c r="P6" t="n">
-        <v>385.2431651901932</v>
+        <v>385.3009179751896</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33324,28 +33391,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1094913441854067</v>
+        <v>-0.1167998627145546</v>
       </c>
       <c r="J7" t="n">
+        <v>473</v>
+      </c>
+      <c r="K7" t="n">
         <v>472</v>
       </c>
-      <c r="K7" t="n">
-        <v>471</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.007532894886154495</v>
+        <v>0.00853888807934633</v>
       </c>
       <c r="M7" t="n">
-        <v>7.25364406189405</v>
+        <v>7.276663197105196</v>
       </c>
       <c r="N7" t="n">
-        <v>90.73987345173354</v>
+        <v>91.22189831838331</v>
       </c>
       <c r="O7" t="n">
-        <v>9.525747920858159</v>
+        <v>9.551015564765001</v>
       </c>
       <c r="P7" t="n">
-        <v>381.7097915940084</v>
+        <v>381.7870282674199</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33402,28 +33469,28 @@
         <v>0.0788</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1354065293006768</v>
+        <v>-0.1373072896258892</v>
       </c>
       <c r="J8" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K8" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01284897958012565</v>
+        <v>0.01325951391724811</v>
       </c>
       <c r="M8" t="n">
-        <v>7.477312368411966</v>
+        <v>7.4731528498265</v>
       </c>
       <c r="N8" t="n">
-        <v>81.06762541631645</v>
+        <v>80.94192175295534</v>
       </c>
       <c r="O8" t="n">
-        <v>9.003756183744452</v>
+        <v>8.996772852137333</v>
       </c>
       <c r="P8" t="n">
-        <v>381.6705790628288</v>
+        <v>381.690626784424</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33480,28 +33547,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2196145575227292</v>
+        <v>-0.2183464958932521</v>
       </c>
       <c r="J9" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K9" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03098539123571142</v>
+        <v>0.03076801702392895</v>
       </c>
       <c r="M9" t="n">
-        <v>7.542502041890416</v>
+        <v>7.533586624909375</v>
       </c>
       <c r="N9" t="n">
-        <v>86.80582499009763</v>
+        <v>86.6426368170394</v>
       </c>
       <c r="O9" t="n">
-        <v>9.316964365612742</v>
+        <v>9.308202663083749</v>
       </c>
       <c r="P9" t="n">
-        <v>375.4462578224095</v>
+        <v>375.4328833079185</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33558,28 +33625,28 @@
         <v>0.1006</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5905406945615503</v>
+        <v>-0.5887369076856156</v>
       </c>
       <c r="J10" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K10" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2005084300041697</v>
+        <v>0.2001749600909564</v>
       </c>
       <c r="M10" t="n">
-        <v>7.29520371454611</v>
+        <v>7.290039702760717</v>
       </c>
       <c r="N10" t="n">
-        <v>80.02656806334208</v>
+        <v>79.89852257630092</v>
       </c>
       <c r="O10" t="n">
-        <v>8.9457569866022</v>
+        <v>8.938597349489511</v>
       </c>
       <c r="P10" t="n">
-        <v>376.281860660541</v>
+        <v>376.2628357384473</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33636,28 +33703,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4216596791358171</v>
+        <v>-0.4237182507062144</v>
       </c>
       <c r="J11" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K11" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1100227917668161</v>
+        <v>0.1113658713233141</v>
       </c>
       <c r="M11" t="n">
-        <v>7.408609263868307</v>
+        <v>7.403009117961647</v>
       </c>
       <c r="N11" t="n">
-        <v>82.77013263341782</v>
+        <v>82.64873081710854</v>
       </c>
       <c r="O11" t="n">
-        <v>9.097809221643297</v>
+        <v>9.091134737595112</v>
       </c>
       <c r="P11" t="n">
-        <v>373.2038876615454</v>
+        <v>373.2255998517567</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33714,28 +33781,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6446962705298237</v>
+        <v>-0.6424035839007336</v>
       </c>
       <c r="J12" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K12" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2573027430586131</v>
+        <v>0.256627301635986</v>
       </c>
       <c r="M12" t="n">
-        <v>6.813930330908522</v>
+        <v>6.811837222863094</v>
       </c>
       <c r="N12" t="n">
-        <v>69.04480362036199</v>
+        <v>68.96530128397156</v>
       </c>
       <c r="O12" t="n">
-        <v>8.309320286302725</v>
+        <v>8.304534983006066</v>
       </c>
       <c r="P12" t="n">
-        <v>379.0338090570882</v>
+        <v>379.009627605784</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33792,28 +33859,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4864049084286532</v>
+        <v>-0.485565144631009</v>
       </c>
       <c r="J13" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K13" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1302028174319716</v>
+        <v>0.1303158460487777</v>
       </c>
       <c r="M13" t="n">
-        <v>7.70625617300707</v>
+        <v>7.694867292812144</v>
       </c>
       <c r="N13" t="n">
-        <v>90.95923341246362</v>
+        <v>90.77584821498235</v>
       </c>
       <c r="O13" t="n">
-        <v>9.537255025030191</v>
+        <v>9.527636024480698</v>
       </c>
       <c r="P13" t="n">
-        <v>380.8220406048936</v>
+        <v>380.8131834383179</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33870,28 +33937,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3800550732779919</v>
+        <v>-0.3820589405883373</v>
       </c>
       <c r="J14" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K14" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08637604326720416</v>
+        <v>0.08752565040690174</v>
       </c>
       <c r="M14" t="n">
-        <v>7.866847554839163</v>
+        <v>7.860989197664445</v>
       </c>
       <c r="N14" t="n">
-        <v>88.14659295511836</v>
+        <v>88.01044964638852</v>
       </c>
       <c r="O14" t="n">
-        <v>9.388641699155334</v>
+        <v>9.381388471137337</v>
       </c>
       <c r="P14" t="n">
-        <v>383.534303812091</v>
+        <v>383.5554352921263</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33948,28 +34015,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2215044011147309</v>
+        <v>-0.2161710943846286</v>
       </c>
       <c r="J15" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K15" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02643905074894526</v>
+        <v>0.02523899541947838</v>
       </c>
       <c r="M15" t="n">
-        <v>8.313687059426544</v>
+        <v>8.322921882190711</v>
       </c>
       <c r="N15" t="n">
-        <v>104.5767397846342</v>
+        <v>104.7168965730694</v>
       </c>
       <c r="O15" t="n">
-        <v>10.22627692685047</v>
+        <v>10.23312740920728</v>
       </c>
       <c r="P15" t="n">
-        <v>387.8480752136478</v>
+        <v>387.7918792485602</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34026,28 +34093,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3413044924024208</v>
+        <v>-0.3339348031763725</v>
       </c>
       <c r="J16" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K16" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L16" t="n">
-        <v>0.042279939986543</v>
+        <v>0.04054649745339978</v>
       </c>
       <c r="M16" t="n">
-        <v>10.22242394550169</v>
+        <v>10.23464505853047</v>
       </c>
       <c r="N16" t="n">
-        <v>152.8282440091991</v>
+        <v>153.1961457504601</v>
       </c>
       <c r="O16" t="n">
-        <v>12.36237210284495</v>
+        <v>12.37724305935939</v>
       </c>
       <c r="P16" t="n">
-        <v>395.6544491586064</v>
+        <v>395.576765592817</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34085,7 +34152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q473"/>
+  <dimension ref="A1:Q474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75179,6 +75246,93 @@
         </is>
       </c>
     </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>-45.503988228760555,166.7181895266847</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>-45.50347857402039,166.71873914181518</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>-45.50295751754146,166.71927376613235</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-45.502561974299596,166.71997346643985</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>-45.502209319530124,166.7207295786031</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>-45.501781011210255,166.7213793472853</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>-45.50125081085071,166.72184195598757</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>-45.5007496516069,166.72233769807735</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>-45.50027280346661,166.7229244820279</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>-45.49979709558057,166.72351339335856</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>-45.49922135306151,166.72391302129927</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>-45.498689463685444,166.72438006288306</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>-45.498163703907956,166.7248595627157</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>-45.49749161814872,166.72504936035807</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>-45.49690593373181,166.72541780486415</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
